--- a/data/trans_dic/P32E$bar_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 100,0</t>
+          <t>23,37; 100,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,37; 100,0</t>
+          <t>27,15; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,95; 100,0</t>
+          <t>34,51; 100,0</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,62; 97,63</t>
+          <t>61,46; 97,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,66; 94,36</t>
+          <t>59,21; 95,52</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,64; 93,13</t>
+          <t>22,59; 92,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,82; 96,71</t>
+          <t>54,0; 95,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,02; 89,66</t>
+          <t>52,98; 91,38</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,24; 100,0</t>
+          <t>32,82; 100,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,56; 89,6</t>
+          <t>54,18; 89,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,7; 100,0</t>
+          <t>46,71; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,09; 90,22</t>
+          <t>60,73; 89,18</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,93; 75,18</t>
+          <t>41,72; 76,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,33; 85,53</t>
+          <t>32,24; 86,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42,86; 73,84</t>
+          <t>44,36; 74,8</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,05; 70,97</t>
+          <t>38,8; 71,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,96; 89,46</t>
+          <t>49,92; 89,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,93; 73,03</t>
+          <t>46,89; 73,82</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57,44; 74,16</t>
+          <t>58,04; 75,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>58,81; 83,98</t>
+          <t>59,73; 84,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61,77; 74,96</t>
+          <t>61,79; 75,46</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1733; 2718</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1302; 5547</t>
+          <t>1296; 5547</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2788; 10188</t>
+          <t>2766; 10188</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>812; 1885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3858; 12073</t>
+          <t>4166; 12073</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9094; 14644</t>
+          <t>9219; 14668</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9537; 15085</t>
+          <t>9466; 15271</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2712; 10250</t>
+          <t>2486; 10184</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5550; 9971</t>
+          <t>5568; 9892</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11516; 19115</t>
+          <t>11294; 19479</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1421; 2556</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 310</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1061; 3100</t>
+          <t>1017; 3100</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14978; 24597</t>
+          <t>14875; 24631</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3078; 7043</t>
+          <t>3290; 7043</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21764; 31121</t>
+          <t>20947; 30762</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13816; 24775</t>
+          <t>13749; 25078</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4485; 13079</t>
+          <t>4930; 13213</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20679; 35627</t>
+          <t>21404; 36089</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>16028; 29892</t>
+          <t>16343; 29949</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8280; 14256</t>
+          <t>7956; 14190</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27247; 42399</t>
+          <t>27221; 42857</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>82776; 106876</t>
+          <t>83638; 108288</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>32177; 45948</t>
+          <t>32683; 46372</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>122822; 149033</t>
+          <t>122849; 150025</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$bar_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Provincia-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,37; 100,0</t>
+          <t>40,76; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,15; 100,0</t>
+          <t>26,52; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,51; 100,0</t>
+          <t>36,71; 100,0</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,46; 97,79</t>
+          <t>49,78; 94,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,21; 95,52</t>
+          <t>50,17; 90,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,59; 92,53</t>
+          <t>25,61; 93,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,0; 95,93</t>
+          <t>48,83; 95,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,98; 91,38</t>
+          <t>53,38; 91,18</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,82; 100,0</t>
+          <t>27,66; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54,18; 89,72</t>
+          <t>57,83; 90,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,71; 100,0</t>
+          <t>46,01; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60,73; 89,18</t>
+          <t>64,42; 91,31</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,25%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,72; 76,1</t>
+          <t>44,81; 76,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,24; 86,41</t>
+          <t>33,11; 83,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,36; 74,8</t>
+          <t>45,84; 73,27</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,8; 71,1</t>
+          <t>38,06; 71,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,92; 89,04</t>
+          <t>46,43; 89,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,89; 73,82</t>
+          <t>45,12; 73,17</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58,04; 75,14</t>
+          <t>56,91; 72,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>59,73; 84,75</t>
+          <t>58,67; 81,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61,79; 75,46</t>
+          <t>60,83; 73,8</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4966</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2829</t>
+          <t>0; 2681</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1296; 5547</t>
+          <t>2624; 6437</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9085</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2766; 10188</t>
+          <t>2650; 9993</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4166; 12073</t>
+          <t>4331; 11797</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12639</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9219; 14668</t>
+          <t>8082; 15305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9466; 15271</t>
+          <t>8618; 15485</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>17602</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2486; 10184</t>
+          <t>3034; 11129</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5568; 9892</t>
+          <t>5654; 11004</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11294; 19479</t>
+          <t>12503; 21357</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2764</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1017; 3100</t>
+          <t>999; 3613</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27443</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14875; 24631</t>
+          <t>15780; 24757</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3290; 7043</t>
+          <t>3284; 7137</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20947; 30762</t>
+          <t>22176; 31434</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>38931</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13749; 25078</t>
+          <t>19676; 33584</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4930; 13213</t>
+          <t>6506; 16490</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21404; 36089</t>
+          <t>29138; 46571</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>25734</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>38970</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>16343; 29949</t>
+          <t>17801; 33268</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7956; 14190</t>
+          <t>8578; 16479</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27221; 42857</t>
+          <t>29437; 47736</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>152399</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>83638; 108288</t>
+          <t>91893; 117638</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>32683; 46372</t>
+          <t>37657; 52305</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>122849; 150025</t>
+          <t>137276; 166546</t>
         </is>
       </c>
     </row>
